--- a/artfynd/A 37322-2022 artfynd.xlsx
+++ b/artfynd/A 37322-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581360</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130581363</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130581357</v>
       </c>
       <c r="B4" t="n">
-        <v>80289</v>
+        <v>80315</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130581359</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>130581364</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130581361</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130581367</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>130581366</v>
       </c>
       <c r="B9" t="n">
-        <v>80289</v>
+        <v>80315</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>130581368</v>
       </c>
       <c r="B10" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>130581362</v>
       </c>
       <c r="B11" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>130581365</v>
       </c>
       <c r="B12" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37322-2022 artfynd.xlsx
+++ b/artfynd/A 37322-2022 artfynd.xlsx
@@ -1646,7 +1646,7 @@
         <v>130581362</v>
       </c>
       <c r="B11" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37322-2022 artfynd.xlsx
+++ b/artfynd/A 37322-2022 artfynd.xlsx
@@ -1646,7 +1646,7 @@
         <v>130581362</v>
       </c>
       <c r="B11" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37322-2022 artfynd.xlsx
+++ b/artfynd/A 37322-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581360</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130581363</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130581357</v>
       </c>
       <c r="B4" t="n">
-        <v>80315</v>
+        <v>80317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130581359</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>130581364</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130581361</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130581367</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>130581366</v>
       </c>
       <c r="B9" t="n">
-        <v>80315</v>
+        <v>80317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>130581368</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>130581362</v>
       </c>
       <c r="B11" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>130581365</v>
       </c>
       <c r="B12" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37322-2022 artfynd.xlsx
+++ b/artfynd/A 37322-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581360</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130581363</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130581357</v>
       </c>
       <c r="B4" t="n">
-        <v>80317</v>
+        <v>80325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130581359</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>130581364</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130581361</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130581367</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>130581366</v>
       </c>
       <c r="B9" t="n">
-        <v>80317</v>
+        <v>80325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>130581368</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>130581362</v>
       </c>
       <c r="B11" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>130581365</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37322-2022 artfynd.xlsx
+++ b/artfynd/A 37322-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581360</v>
       </c>
       <c r="B2" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130581363</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130581357</v>
       </c>
       <c r="B4" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130581359</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>130581364</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130581361</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130581367</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>130581366</v>
       </c>
       <c r="B9" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>130581368</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>130581362</v>
       </c>
       <c r="B11" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>130581365</v>
       </c>
       <c r="B12" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37322-2022 artfynd.xlsx
+++ b/artfynd/A 37322-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581360</v>
       </c>
       <c r="B2" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130581363</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130581357</v>
       </c>
       <c r="B4" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130581359</v>
       </c>
       <c r="B5" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>130581364</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130581361</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130581367</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>130581366</v>
       </c>
       <c r="B9" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>130581368</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>130581362</v>
       </c>
       <c r="B11" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>130581365</v>
       </c>
       <c r="B12" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37322-2022 artfynd.xlsx
+++ b/artfynd/A 37322-2022 artfynd.xlsx
@@ -1646,7 +1646,7 @@
         <v>130581362</v>
       </c>
       <c r="B11" t="n">
-        <v>91796</v>
+        <v>91804</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37322-2022 artfynd.xlsx
+++ b/artfynd/A 37322-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130581360</v>
+        <v>130581357</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lagmyrliden, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557194</v>
+        <v>557207</v>
       </c>
       <c r="R2" t="n">
-        <v>7191217</v>
+        <v>7191185</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130581363</v>
+        <v>130581366</v>
       </c>
       <c r="B3" t="n">
-        <v>79243</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557019</v>
+        <v>557120</v>
       </c>
       <c r="R3" t="n">
-        <v>7191398</v>
+        <v>7191188</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130581357</v>
+        <v>130581359</v>
       </c>
       <c r="B4" t="n">
-        <v>80349</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1001,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130581359</v>
+        <v>130581361</v>
       </c>
       <c r="B5" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557207</v>
+        <v>557066</v>
       </c>
       <c r="R5" t="n">
-        <v>7191185</v>
+        <v>7191578</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130581364</v>
+        <v>130581363</v>
       </c>
       <c r="B6" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557074</v>
+        <v>557019</v>
       </c>
       <c r="R6" t="n">
-        <v>7191354</v>
+        <v>7191398</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130581361</v>
+        <v>130581364</v>
       </c>
       <c r="B7" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557066</v>
+        <v>557074</v>
       </c>
       <c r="R7" t="n">
-        <v>7191578</v>
+        <v>7191354</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130581367</v>
+        <v>130581365</v>
       </c>
       <c r="B8" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557120</v>
+        <v>557116</v>
       </c>
       <c r="R8" t="n">
-        <v>7191188</v>
+        <v>7191281</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130581366</v>
+        <v>130581367</v>
       </c>
       <c r="B9" t="n">
-        <v>80349</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1539,11 +1534,11 @@
         <v>130581368</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1643,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130581362</v>
+        <v>130581360</v>
       </c>
       <c r="B11" t="n">
-        <v>91828</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,30 +1649,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lagmyrliden, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557019</v>
+        <v>557194</v>
       </c>
       <c r="R11" t="n">
-        <v>7191398</v>
+        <v>7191217</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1709,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1719,7 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,113 +1747,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>130581365</v>
-      </c>
-      <c r="B12" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Lagmyrliden, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>557116</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7191281</v>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
